--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78856</v>
+        <v>78858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78856</v>
+        <v>78858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79519</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>136007802</v>
       </c>
       <c r="B23" t="n">
-        <v>58844</v>
+        <v>58846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78858</v>
+        <v>78859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78858</v>
+        <v>78859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78859</v>
+        <v>78860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78859</v>
+        <v>78860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>136007802</v>
       </c>
       <c r="B23" t="n">
-        <v>58846</v>
+        <v>58847</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78860</v>
+        <v>78864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78860</v>
+        <v>78864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79523</v>
+        <v>79527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>136007802</v>
       </c>
       <c r="B23" t="n">
-        <v>58847</v>
+        <v>58851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78864</v>
+        <v>78865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78864</v>
+        <v>78865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79527</v>
+        <v>79528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>136007802</v>
       </c>
       <c r="B23" t="n">
-        <v>58851</v>
+        <v>58852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78865</v>
+        <v>78869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78865</v>
+        <v>78869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79528</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>per-erik mukka, Christina Boyd</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78869</v>
+        <v>78875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78869</v>
+        <v>78875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79538</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>136007802</v>
       </c>
       <c r="B23" t="n">
-        <v>58852</v>
+        <v>58857</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78875</v>
+        <v>78888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78875</v>
+        <v>78888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79538</v>
+        <v>79551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78464</v>
+        <v>78477</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>136007802</v>
       </c>
       <c r="B23" t="n">
-        <v>58857</v>
+        <v>58870</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 30524-2026 artfynd.xlsx
+++ b/artfynd/A 30524-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136007811</v>
       </c>
       <c r="B2" t="n">
-        <v>78888</v>
+        <v>78889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136007813</v>
       </c>
       <c r="B3" t="n">
-        <v>78888</v>
+        <v>78889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136007812</v>
       </c>
       <c r="B4" t="n">
-        <v>79551</v>
+        <v>79552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136007789</v>
       </c>
       <c r="B5" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136007790</v>
       </c>
       <c r="B6" t="n">
-        <v>79552</v>
+        <v>79553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>136007787</v>
       </c>
       <c r="B7" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136007580</v>
       </c>
       <c r="B8" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136007581</v>
       </c>
       <c r="B9" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>136007582</v>
       </c>
       <c r="B10" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>136007770</v>
       </c>
       <c r="B11" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>136007773</v>
       </c>
       <c r="B12" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136007791</v>
       </c>
       <c r="B13" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>136007803</v>
       </c>
       <c r="B14" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>136007810</v>
       </c>
       <c r="B15" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>136007785</v>
       </c>
       <c r="B16" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>136007781</v>
       </c>
       <c r="B17" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>136007808</v>
       </c>
       <c r="B18" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>136007775</v>
       </c>
       <c r="B19" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>136007780</v>
       </c>
       <c r="B20" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>136007814</v>
       </c>
       <c r="B21" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>136007786</v>
       </c>
       <c r="B22" t="n">
-        <v>78477</v>
+        <v>78478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
